--- a/data/team.xlsx
+++ b/data/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solisservices-my.sharepoint.com/personal/l_jo_uu_nl/Documents/PSR/WEBSITE/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{2ECD8549-4FAB-D64C-896B-4476142CAE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EEB0E8C-BAB2-A64E-898E-CF1855EA4A00}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{2ECD8549-4FAB-D64C-896B-4476142CAE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26DD60B9-3940-DF4F-A311-8AE6AAD8383D}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16900" xr2:uid="{AC0D33F6-FE1F-474A-AAEA-EAE863AC9E26}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="29">
   <si>
     <t>position</t>
   </si>
@@ -104,8 +104,25 @@
     <t>description</t>
   </si>
   <si>
-    <t>I'm an assistant professor in the Plant Stress Resilience group at Utrecht University’s Faculty of Science. I'm curious about molecular and genetic mechanisms that control plant development and stress responses. My research combines experimental and computational approaches to understand gene regulatory networks in plants. I completed my bachelors and masters in the Biosciences Institute at the University of Sao Paulo, Brazil under the supervision of Prof. Eny Floh. I then followed to pursue a phd in the plant biology graduate group at UC Davis being supervised by Prof. John Harada. Afterwards, I moved to the Netherlands and started a postdoc in the group of  Prof. Kaisa Kajala (Utrecht University) followed by another postdoc in the group of Ronald Pierik (Wageningen University). 
-I was born and raised in Sao Paulo Brazil and I'm a son of south korean imigrants and I lived in many different parts of the world (US and the NL). I enjoy spending time with my wife, playing video games and watching TV series.</t>
+    <t>postdoc</t>
+  </si>
+  <si>
+    <t>Jim Halpert</t>
+  </si>
+  <si>
+    <t>images/lab_members/jimhalpert.jpeg</t>
+  </si>
+  <si>
+    <t>nl</t>
+  </si>
+  <si>
+    <t>Postdoctoral Fellow</t>
+  </si>
+  <si>
+    <t>alumni</t>
+  </si>
+  <si>
+    <t>James Duncan Halpert[3] is a fictional character in the American version of the television sitcom The Office, portrayed by John Krasinski. He is introduced as a sales representative at the Scranton branch of paper distribution company Dunder Mifflin, before temporarily transferring to the Stamford branch in the third season. Upon the merger of Scranton and Stamford branches, he becomes Assistant Regional Manager, and later co-manager alongside Michael Scott during the sixth-season episode arc from "The Promotion" to "The Manager and the Salesman". The character is based on Tim Canterbury from the original version of The Office.</t>
   </si>
 </sst>
 </file>
@@ -150,10 +167,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -489,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFC1B41B-A9AD-9442-9B45-C55C0DC202EF}">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" bestFit="1" customWidth="1"/>
@@ -565,8 +581,8 @@
       <c r="H2" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>22</v>
+      <c r="I2" t="s">
+        <v>28</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>16</v>
@@ -579,28 +595,225 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G3" s="1"/>
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3">
+        <v>2026</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" t="s">
+        <v>28</v>
+      </c>
       <c r="J3" s="1"/>
+      <c r="K3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G4" s="1"/>
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4">
+        <v>2026</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
+        <v>28</v>
+      </c>
       <c r="J4" s="1"/>
+      <c r="K4" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G5" s="1"/>
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5">
+        <v>2026</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" t="s">
+        <v>28</v>
+      </c>
       <c r="J5" s="1"/>
+      <c r="K5" t="s">
+        <v>15</v>
+      </c>
+      <c r="L5" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G6" s="1"/>
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6">
+        <v>2026</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" t="s">
+        <v>28</v>
+      </c>
       <c r="J6" s="1"/>
+      <c r="K6" t="s">
+        <v>15</v>
+      </c>
+      <c r="L6" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G7" s="1"/>
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7">
+        <v>2026</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" t="s">
+        <v>28</v>
+      </c>
       <c r="J7" s="1"/>
+      <c r="K7" t="s">
+        <v>15</v>
+      </c>
+      <c r="L7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8">
+        <v>2026</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L8" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{0880E996-2E97-0B4C-8A18-657277620DA0}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{85B66FB1-5A88-F740-9FB5-A9501873B675}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/team.xlsx
+++ b/data/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solisservices-my.sharepoint.com/personal/l_jo_uu_nl/Documents/PSR/WEBSITE/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{2ECD8549-4FAB-D64C-896B-4476142CAE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26DD60B9-3940-DF4F-A311-8AE6AAD8383D}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{2ECD8549-4FAB-D64C-896B-4476142CAE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95D9E79B-1C42-9B44-A292-03A4E39A3307}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16900" xr2:uid="{AC0D33F6-FE1F-474A-AAEA-EAE863AC9E26}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
   <si>
     <t>position</t>
   </si>
@@ -104,22 +104,7 @@
     <t>description</t>
   </si>
   <si>
-    <t>postdoc</t>
-  </si>
-  <si>
-    <t>Jim Halpert</t>
-  </si>
-  <si>
-    <t>images/lab_members/jimhalpert.jpeg</t>
-  </si>
-  <si>
     <t>nl</t>
-  </si>
-  <si>
-    <t>Postdoctoral Fellow</t>
-  </si>
-  <si>
-    <t>alumni</t>
   </si>
   <si>
     <t>James Duncan Halpert[3] is a fictional character in the American version of the television sitcom The Office, portrayed by John Krasinski. He is introduced as a sales representative at the Scranton branch of paper distribution company Dunder Mifflin, before temporarily transferring to the Stamford branch in the third season. Upon the merger of Scranton and Stamford branches, he becomes Assistant Regional Manager, and later co-manager alongside Michael Scott during the sixth-season episode arc from "The Promotion" to "The Manager and the Salesman". The character is based on Tim Canterbury from the original version of The Office.</t>
@@ -582,7 +567,7 @@
         <v>7</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>16</v>
@@ -595,225 +580,68 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3">
-        <v>2026</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" t="s">
-        <v>28</v>
-      </c>
+      <c r="G3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" t="s">
         <v>15</v>
       </c>
       <c r="L3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4">
-        <v>2026</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" t="s">
-        <v>28</v>
-      </c>
+      <c r="G4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" t="s">
         <v>15</v>
       </c>
       <c r="L4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5">
-        <v>2026</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" t="s">
-        <v>28</v>
-      </c>
+      <c r="G5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" t="s">
         <v>15</v>
       </c>
       <c r="L5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6">
-        <v>2026</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" t="s">
-        <v>28</v>
-      </c>
+      <c r="G6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" t="s">
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7">
-        <v>2026</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" t="s">
-        <v>28</v>
-      </c>
+      <c r="G7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" t="s">
         <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8">
-        <v>2026</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H8" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" t="s">
-        <v>28</v>
-      </c>
+      <c r="G8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" t="s">
         <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{0880E996-2E97-0B4C-8A18-657277620DA0}"/>
-    <hyperlink ref="G3" r:id="rId2" xr:uid="{85B66FB1-5A88-F740-9FB5-A9501873B675}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/team.xlsx
+++ b/data/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solisservices-my.sharepoint.com/personal/l_jo_uu_nl/Documents/PSR/WEBSITE/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{2ECD8549-4FAB-D64C-896B-4476142CAE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95D9E79B-1C42-9B44-A292-03A4E39A3307}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="8_{2ECD8549-4FAB-D64C-896B-4476142CAE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B900B734-C636-5A40-9BD2-2A122057163A}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16900" xr2:uid="{AC0D33F6-FE1F-474A-AAEA-EAE863AC9E26}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>position</t>
   </si>
@@ -104,10 +104,8 @@
     <t>description</t>
   </si>
   <si>
-    <t>nl</t>
-  </si>
-  <si>
-    <t>James Duncan Halpert[3] is a fictional character in the American version of the television sitcom The Office, portrayed by John Krasinski. He is introduced as a sales representative at the Scranton branch of paper distribution company Dunder Mifflin, before temporarily transferring to the Stamford branch in the third season. Upon the merger of Scranton and Stamford branches, he becomes Assistant Regional Manager, and later co-manager alongside Michael Scott during the sixth-season episode arc from "The Promotion" to "The Manager and the Salesman". The character is based on Tim Canterbury from the original version of The Office.</t>
+    <t>I'm an assistant professor in the Plant Stress Resilience group at Utrecht University’s Faculty of Science. I'm curious about molecular and genetic mechanisms that control plant development and stress responses. My research combines experimental and computational approaches to understand gene regulatory networks in plants. I completed my bachelors and masters in the Biosciences Institute at the University of Sao Paulo, Brazil under the supervision of Prof. Eny Floh. I then followed to pursue a phd in the plant biology graduate group at UC Davis being supervised by Prof. John Harada. Afterwards, I moved to the Netherlands and started a postdoc in the group of  Prof. Kaisa Kajala (Utrecht University) followed by another postdoc in the group of Ronald Pierik (Wageningen University). 
+I was born and raised in Sao Paulo Brazil and I'm a son of south korean imigrants and I lived in many different parts of the world (US and the NL). I enjoy spending time with my wife, playing video games and watching TV series.</t>
   </si>
 </sst>
 </file>
@@ -490,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFC1B41B-A9AD-9442-9B45-C55C0DC202EF}">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" bestFit="1" customWidth="1"/>
@@ -567,7 +565,7 @@
         <v>7</v>
       </c>
       <c r="I2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>16</v>
@@ -577,66 +575,6 @@
       </c>
       <c r="L2" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" t="s">
-        <v>15</v>
-      </c>
-      <c r="L6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" t="s">
-        <v>15</v>
-      </c>
-      <c r="L7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" t="s">
-        <v>15</v>
-      </c>
-      <c r="L8" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/data/team.xlsx
+++ b/data/team.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solisservices-my.sharepoint.com/personal/l_jo_uu_nl/Documents/PSR/WEBSITE/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="8_{2ECD8549-4FAB-D64C-896B-4476142CAE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B900B734-C636-5A40-9BD2-2A122057163A}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="8_{2ECD8549-4FAB-D64C-896B-4476142CAE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB381379-5EC3-C047-BEB3-B0AE2E2BCAF3}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16900" xr2:uid="{AC0D33F6-FE1F-474A-AAEA-EAE863AC9E26}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>position</t>
   </si>
@@ -106,6 +106,30 @@
   <si>
     <t>I'm an assistant professor in the Plant Stress Resilience group at Utrecht University’s Faculty of Science. I'm curious about molecular and genetic mechanisms that control plant development and stress responses. My research combines experimental and computational approaches to understand gene regulatory networks in plants. I completed my bachelors and masters in the Biosciences Institute at the University of Sao Paulo, Brazil under the supervision of Prof. Eny Floh. I then followed to pursue a phd in the plant biology graduate group at UC Davis being supervised by Prof. John Harada. Afterwards, I moved to the Netherlands and started a postdoc in the group of  Prof. Kaisa Kajala (Utrecht University) followed by another postdoc in the group of Ronald Pierik (Wageningen University). 
 I was born and raised in Sao Paulo Brazil and I'm a son of south korean imigrants and I lived in many different parts of the world (US and the NL). I enjoy spending time with my wife, playing video games and watching TV series.</t>
+  </si>
+  <si>
+    <t>bachelor</t>
+  </si>
+  <si>
+    <t>I'm a third-year student Molecular and Biophysical Life Sciences at Utrecht University and am currently doing my internship at Leonardo's lab. My main interest lies in using bioinformatics to see how plants and microorganisms adapt their genomes and transcriptomes to changing environments, whether it be in response to stress or on a larger, evolutionary scale. During my internship, I will use a single-cell RNA-seq dataset to analyze the promoters of cell-type-specific genes in Arabidopsis roots. The goal is to find motifs that could explain why different cell types develop and respond in unique ways. In my free time, I like playing games, playing the piano, learning about shiny new hobbies, and taking nice walks.</t>
+  </si>
+  <si>
+    <t>nl</t>
+  </si>
+  <si>
+    <t>f.j.douwes@students.uu.nl</t>
+  </si>
+  <si>
+    <t>images/lab_members/fiekedouwes.png</t>
+  </si>
+  <si>
+    <t>Bachelor Intern</t>
+  </si>
+  <si>
+    <t>April 2026</t>
+  </si>
+  <si>
+    <t>Fieke J. Douwes</t>
   </si>
 </sst>
 </file>
@@ -150,9 +174,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -488,12 +513,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFC1B41B-A9AD-9442-9B45-C55C0DC202EF}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="29.33203125" customWidth="1"/>
+    <col min="3" max="3" width="29.33203125" style="2" customWidth="1"/>
+    <col min="4" max="5" width="29.33203125" customWidth="1"/>
     <col min="6" max="6" width="32.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.83203125" bestFit="1" customWidth="1"/>
@@ -508,7 +534,7 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D1" t="s">
@@ -546,7 +572,7 @@
       <c r="B2" t="s">
         <v>17</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>2026</v>
       </c>
       <c r="D2" t="s">
@@ -575,6 +601,38 @@
       </c>
       <c r="L2" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/data/team.xlsx
+++ b/data/team.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solisservices-my.sharepoint.com/personal/l_jo_uu_nl/Documents/PSR/WEBSITE/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="8_{2ECD8549-4FAB-D64C-896B-4476142CAE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB381379-5EC3-C047-BEB3-B0AE2E2BCAF3}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="8_{2ECD8549-4FAB-D64C-896B-4476142CAE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{490CC806-356D-2A45-B5EF-65078B363618}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16900" xr2:uid="{AC0D33F6-FE1F-474A-AAEA-EAE863AC9E26}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>position</t>
   </si>
@@ -130,6 +130,9 @@
   </si>
   <si>
     <t>Fieke J. Douwes</t>
+  </si>
+  <si>
+    <t>July 2026</t>
   </si>
 </sst>
 </file>
@@ -518,8 +521,8 @@
   <cols>
     <col min="1" max="1" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.33203125" style="2" customWidth="1"/>
-    <col min="4" max="5" width="29.33203125" customWidth="1"/>
+    <col min="3" max="4" width="29.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="29.33203125" customWidth="1"/>
     <col min="6" max="6" width="32.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.83203125" bestFit="1" customWidth="1"/>
@@ -537,7 +540,7 @@
       <c r="C1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E1" t="s">
@@ -575,7 +578,7 @@
       <c r="C2" s="2">
         <v>2026</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E2" t="s">
@@ -613,8 +616,8 @@
       <c r="C3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D3" t="s">
-        <v>12</v>
+      <c r="D3" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>28</v>

--- a/data/team.xlsx
+++ b/data/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solisservices-my.sharepoint.com/personal/l_jo_uu_nl/Documents/PSR/WEBSITE/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{2ECD8549-4FAB-D64C-896B-4476142CAE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{490CC806-356D-2A45-B5EF-65078B363618}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="8_{2ECD8549-4FAB-D64C-896B-4476142CAE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5749D83F-2FC9-A54F-B20A-E6935282F74A}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16900" xr2:uid="{AC0D33F6-FE1F-474A-AAEA-EAE863AC9E26}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>position</t>
   </si>
@@ -133,6 +133,9 @@
   </si>
   <si>
     <t>July 2026</t>
+  </si>
+  <si>
+    <t>alumni</t>
   </si>
 </sst>
 </file>
@@ -629,7 +632,7 @@
         <v>26</v>
       </c>
       <c r="H3" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="I3" t="s">
         <v>24</v>
